--- a/data/trans_dic/P1414-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1414-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,08</t>
+          <t>1,04; 4,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,62</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,86</t>
+          <t>1,43; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,13</t>
+          <t>0,41; 2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,99</t>
+          <t>0,47; 2,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,02</t>
+          <t>0,73; 2,03</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,94</t>
+          <t>0,29; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,43</t>
+          <t>0,57; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,06</t>
+          <t>2,27; 5,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,45</t>
+          <t>0,26; 1,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,1</t>
+          <t>0,5; 2,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,51</t>
+          <t>1,12; 2,49</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,51</t>
+          <t>0,18; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,42</t>
+          <t>0,61; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,96</t>
+          <t>2,45; 7,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,68</t>
+          <t>1,82; 7,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,07</t>
+          <t>3,92; 9,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,34</t>
+          <t>0,81; 2,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,39</t>
+          <t>0,6; 2,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,42</t>
+          <t>1,86; 4,25</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,01</t>
+          <t>0,18; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,46</t>
+          <t>0,63; 2,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,98</t>
+          <t>2,29; 4,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,99</t>
+          <t>2,67; 4,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,13</t>
+          <t>0,35; 1,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,35</t>
+          <t>1,2; 2,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,95</t>
+          <t>1,24; 2,14</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1123,49 +1123,49 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,55</t>
+          <t>2,79; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,67</t>
+          <t>4,82; 8,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,19</t>
+          <t>4,4; 6,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,61</t>
+          <t>1,86; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,09</t>
+          <t>2,68; 4,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,97</t>
+          <t>2,7; 4,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,54</t>
+          <t>1,57; 3,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,96</t>
+          <t>1,82; 3,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,66</t>
+          <t>3,43; 5,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,88</t>
+          <t>1,34; 2,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,07</t>
+          <t>1,53; 3,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,5</t>
+          <t>2,83; 4,68</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,42</t>
+          <t>0,09; 0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,73</t>
+          <t>0,26; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,18</t>
+          <t>2,1; 3,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,23</t>
+          <t>2,91; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,44</t>
+          <t>3,71; 4,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,72</t>
+          <t>1,13; 1,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,41</t>
+          <t>1,66; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,49</t>
+          <t>2,07; 2,63</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12576</t>
         </is>
       </c>
     </row>
@@ -1644,42 +1644,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9036</t>
+          <t>0; 9864</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2966; 15966</t>
+          <t>3257; 15533</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2105; 12549</t>
+          <t>2090; 11808</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6106; 17257</t>
+          <t>6954; 20110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3027; 16037</t>
+          <t>3080; 17077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3187; 15467</t>
+          <t>3672; 16277</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6921; 19174</t>
+          <t>7548; 21041</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>15350</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5711</t>
+          <t>0; 4531</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8100</t>
+          <t>0; 7130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3774</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>972; 9946</t>
+          <t>969; 9845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2072; 12759</t>
+          <t>2111; 13173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8251; 19263</t>
+          <t>9550; 21987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1951; 10974</t>
+          <t>1966; 11859</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2999; 15730</t>
+          <t>3716; 16171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9171; 20865</t>
+          <t>10121; 22488</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>18749</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 4936</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>949; 7880</t>
+          <t>950; 8490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>950; 16136</t>
+          <t>2882; 15838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6314; 20703</t>
+          <t>6384; 20428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2128; 12762</t>
+          <t>3022; 12846</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6795; 16815</t>
+          <t>7352; 17930</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6815; 20825</t>
+          <t>7183; 21354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4186; 16449</t>
+          <t>4106; 16216</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6208; 28531</t>
+          <t>12259; 27979</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>32700</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7880</t>
+          <t>0; 6972</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1980; 11557</t>
+          <t>2049; 10661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>856; 7585</t>
+          <t>866; 7545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4781; 18821</t>
+          <t>4820; 19255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18703; 41162</t>
+          <t>18882; 39757</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12670; 38941</t>
+          <t>22917; 38666</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6366; 21653</t>
+          <t>6724; 23589</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23374; 46397</t>
+          <t>23641; 46780</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19338; 39188</t>
+          <t>24600; 42518</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40025</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>47486</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>965; 8206</t>
+          <t>970; 8199</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5478</t>
+          <t>0; 5524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6089</t>
+          <t>0; 5254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20598; 42203</t>
+          <t>21249; 43297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36884; 64001</t>
+          <t>35594; 62595</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28906; 51738</t>
+          <t>36307; 57666</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23325; 45838</t>
+          <t>23635; 46394</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38709; 69213</t>
+          <t>36446; 65679</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31259; 51963</t>
+          <t>37490; 59114</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>39062</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5793</t>
+          <t>0; 5070</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18184; 39269</t>
+          <t>17437; 39387</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19539; 42843</t>
+          <t>19718; 42923</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26021; 42870</t>
+          <t>28772; 47837</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18309; 39676</t>
+          <t>18409; 40286</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19542; 42059</t>
+          <t>21006; 43296</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26977; 44958</t>
+          <t>30429; 50366</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>136335</t>
+          <t>151156</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>150640</t>
+          <t>165924</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3174; 14426</t>
+          <t>3152; 14867</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7699; 23446</t>
+          <t>7651; 23296</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8267; 24664</t>
+          <t>8985; 25699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73529; 112613</t>
+          <t>74503; 112173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>103977; 149328</t>
+          <t>102872; 150310</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>111149; 158171</t>
+          <t>134032; 174223</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78350; 119938</t>
+          <t>78583; 120244</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>117345; 166762</t>
+          <t>115065; 165482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>126487; 172544</t>
+          <t>145660; 185345</t>
         </is>
       </c>
     </row>
